--- a/KatalonData/IWPTestData/DisplayCFDataDemo.xlsx
+++ b/KatalonData/IWPTestData/DisplayCFDataDemo.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8596" uniqueCount="1272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11076" uniqueCount="1892">
   <si>
     <t>Result</t>
   </si>
@@ -3856,6 +3856,1866 @@
   </si>
   <si>
     <t>Tue Nov 11 06:33:58 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 06:47:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 06:50:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 06:51:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 06:53:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 06:54:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 06:56:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 06:57:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 06:58:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:00:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:02:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:03:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:04:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:06:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:07:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:09:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:10:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:12:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:13:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:15:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:16:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:18:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:19:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:21:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:22:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:24:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:25:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:26:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:28:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:29:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:31:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:32:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:34:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:35:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:37:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:38:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:40:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:41:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:43:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:44:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:46:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:47:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:49:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:50:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:52:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:53:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:55:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:56:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:57:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 07:59:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:00:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:02:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:03:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:07:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:09:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:10:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:11:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:12:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:13:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:14:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:16:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:17:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:19:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:20:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:22:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:23:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:25:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:27:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:28:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:30:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:31:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:32:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:33:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:35:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:35:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:36:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:37:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:38:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:39:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:41:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:42:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:43:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:45:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:46:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:47:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:48:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:50:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:51:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:53:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:55:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:56:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:57:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 08:58:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:00:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:00:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:02:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:03:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:05:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:06:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:07:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:12:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:16:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:17:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:18:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:19:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:21:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:22:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:23:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:25:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:26:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:29:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:30:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:31:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:32:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:34:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:35:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:36:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:38:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:39:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:41:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:42:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:44:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:45:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:47:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:47:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:49:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:51:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:52:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:54:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:55:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:56:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:57:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:58:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 09:59:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:01:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:02:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:04:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:05:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:06:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:07:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:09:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:10:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:12:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:13:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:14:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:16:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:17:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:18:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:19:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:20:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:21:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:23:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:25:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:26:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:27:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:28:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:29:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:30:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:31:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:32:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:34:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:35:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:36:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:37:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:38:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:39:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:40:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:41:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:42:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:43:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:44:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:45:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:46:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:47:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:48:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:50:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:51:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:52:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:53:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:54:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:55:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:56:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:57:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:58:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 10:59:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:00:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:01:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:02:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:03:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:04:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:05:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:06:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:07:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:08:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:10:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:11:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:14:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:16:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:18:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:20:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:21:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:22:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:24:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:26:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:27:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:28:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:31:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:32:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:34:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:35:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:36:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:38:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:40:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:42:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:44:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:45:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:47:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:48:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:50:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:52:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:54:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:55:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:57:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 11:59:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:00:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:02:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:04:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:05:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:07:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:09:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:11:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:12:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:14:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:15:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:17:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:20:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:21:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:23:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:25:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:27:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:28:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:30:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:31:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:33:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:34:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:36:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:37:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:39:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:40:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:42:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:43:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:45:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:46:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:47:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:49:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:51:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:52:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:54:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:55:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:57:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 12:58:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:00:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:01:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:03:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:05:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:06:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:08:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:09:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:11:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:12:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:14:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:17:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:19:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:20:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:22:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:23:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:25:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:26:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:28:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:29:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:31:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:32:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:34:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:36:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:37:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:39:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:40:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:41:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:43:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:45:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:46:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:48:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:49:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:51:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:52:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:54:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:56:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 13:57:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:02:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:06:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:07:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:09:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:11:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:12:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:13:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:26:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:28:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:30:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:33:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:34:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:36:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:37:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:39:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:40:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:42:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:43:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:45:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:46:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:48:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:49:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:51:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:52:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:54:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:55:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:58:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 01:59:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:01:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:02:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:04:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:05:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:07:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:08:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:10:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:11:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:12:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:14:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:15:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:17:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:20:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:21:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:23:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:24:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:26:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:27:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:29:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:31:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:32:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:34:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:35:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:37:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:38:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:40:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:41:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:42:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:47:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:51:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:55:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:56:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:58:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 02:59:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:00:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:01:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:02:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:03:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:05:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:06:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:07:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:09:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:10:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:11:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:12:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:13:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:14:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:15:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:17:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:18:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:20:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:21:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:22:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:24:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:25:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:26:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:28:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:29:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:30:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:31:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:32:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:33:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:34:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:36:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:37:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:39:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:40:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:41:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:43:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:44:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:45:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:47:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:48:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:50:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:52:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:53:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:55:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 03:56:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:00:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:02:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:03:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:05:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:06:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:08:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:10:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:11:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:13:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:14:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:15:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:17:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:18:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:19:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:21:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:22:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:23:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:25:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:26:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:27:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:28:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:30:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:31:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:33:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:34:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:36:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:37:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:39:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:40:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:41:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:42:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:44:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:47:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:48:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:50:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:51:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:53:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:54:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:56:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:57:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 04:58:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:02:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:03:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:05:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:06:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:07:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:08:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:09:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:10:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:11:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:12:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:13:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:14:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:15:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:16:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:17:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:18:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:19:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:21:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:23:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:24:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:25:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:26:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:27:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:28:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:29:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:30:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:31:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:32:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:33:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:34:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:35:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:36:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:37:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:38:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:39:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:40:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:42:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:43:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:44:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:45:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:46:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:47:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:49:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:50:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:51:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:52:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:53:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:54:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:56:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:57:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:58:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 05:59:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:01:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:02:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:04:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:06:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:08:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:09:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:11:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:12:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:14:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:15:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:17:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:19:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:20:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:22:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:24:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:25:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:27:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:28:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:30:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:32:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:33:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:35:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:37:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:38:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:42:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:43:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:45:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:47:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:49:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:50:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:52:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:54:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:56:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:57:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 06:59:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:01:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:05:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:06:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:07:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:09:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:11:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:12:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:14:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:17:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:20:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:22:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:23:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:25:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:26:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:28:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:29:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:31:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:32:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:34:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:35:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:37:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:38:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:40:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:41:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:43:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:45:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:46:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:48:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:49:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:51:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:52:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:54:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:55:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:57:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 07:59:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:01:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:02:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:04:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:05:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:07:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:08:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:10:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:11:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:13:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:15:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:17:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:18:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:20:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:21:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:23:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:24:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:26:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:27:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:29:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:30:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:32:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:33:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:35:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:36:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:38:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:40:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:42:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:43:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:44:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:46:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:47:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:49:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 08:51:11 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -4356,7 +6216,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>966</v>
+        <v>1586</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -4423,7 +6283,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>967</v>
+        <v>1587</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -4490,7 +6350,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>968</v>
+        <v>1588</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -4557,7 +6417,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>969</v>
+        <v>1589</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -4624,7 +6484,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>970</v>
+        <v>1590</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -4691,7 +6551,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>971</v>
+        <v>1591</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -4758,7 +6618,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>972</v>
+        <v>1592</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -4825,7 +6685,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>973</v>
+        <v>1593</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -4892,7 +6752,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>974</v>
+        <v>1594</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -4959,7 +6819,7 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>975</v>
+        <v>1595</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -5026,7 +6886,7 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>976</v>
+        <v>1596</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -5093,7 +6953,7 @@
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>977</v>
+        <v>1597</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -5160,7 +7020,7 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>978</v>
+        <v>1598</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -5227,7 +7087,7 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>979</v>
+        <v>1599</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -5294,7 +7154,7 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>980</v>
+        <v>1600</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -5361,7 +7221,7 @@
         <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>981</v>
+        <v>1601</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -5428,7 +7288,7 @@
         <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>982</v>
+        <v>1602</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -5495,7 +7355,7 @@
         <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>983</v>
+        <v>1603</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -5562,7 +7422,7 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>984</v>
+        <v>1604</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -5629,7 +7489,7 @@
         <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>985</v>
+        <v>1605</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -5696,7 +7556,7 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>986</v>
+        <v>1606</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -5763,7 +7623,7 @@
         <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>987</v>
+        <v>1607</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -5830,7 +7690,7 @@
         <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>988</v>
+        <v>1608</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -5897,7 +7757,7 @@
         <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>989</v>
+        <v>1609</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -5964,7 +7824,7 @@
         <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>990</v>
+        <v>1610</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -6031,7 +7891,7 @@
         <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>991</v>
+        <v>1611</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -6098,7 +7958,7 @@
         <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>992</v>
+        <v>1612</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -6165,7 +8025,7 @@
         <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>993</v>
+        <v>1613</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -6232,7 +8092,7 @@
         <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>994</v>
+        <v>1614</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -6299,7 +8159,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>995</v>
+        <v>1615</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -6366,7 +8226,7 @@
         <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>996</v>
+        <v>1616</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -6433,7 +8293,7 @@
         <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>997</v>
+        <v>1617</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -6500,7 +8360,7 @@
         <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>998</v>
+        <v>1618</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -6567,7 +8427,7 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>999</v>
+        <v>1619</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -6634,7 +8494,7 @@
         <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>1000</v>
+        <v>1620</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -6701,7 +8561,7 @@
         <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>1001</v>
+        <v>1621</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -6768,7 +8628,7 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>1002</v>
+        <v>1622</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -6835,7 +8695,7 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>1003</v>
+        <v>1623</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -6902,7 +8762,7 @@
         <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>1004</v>
+        <v>1624</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -6969,7 +8829,7 @@
         <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>1005</v>
+        <v>1625</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -7036,7 +8896,7 @@
         <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>1006</v>
+        <v>1626</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -7103,7 +8963,7 @@
         <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>1007</v>
+        <v>1627</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -7170,7 +9030,7 @@
         <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>1008</v>
+        <v>1628</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -7237,7 +9097,7 @@
         <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>1009</v>
+        <v>1629</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -7304,7 +9164,7 @@
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>1010</v>
+        <v>1630</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -7371,7 +9231,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>1011</v>
+        <v>1631</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -7438,7 +9298,7 @@
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>1012</v>
+        <v>1632</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -7505,7 +9365,7 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>1013</v>
+        <v>1633</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -7572,7 +9432,7 @@
         <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>1014</v>
+        <v>1634</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>96</v>
@@ -7639,7 +9499,7 @@
         <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>1015</v>
+        <v>1635</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>91</v>
@@ -7703,10 +9563,10 @@
     </row>
     <row ht="115.2" r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>1016</v>
+        <v>1636</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>97</v>
@@ -7895,7 +9755,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1209</v>
+        <v>1829</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -7963,7 +9823,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1210</v>
+        <v>1830</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -8031,7 +9891,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1211</v>
+        <v>1831</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -8099,7 +9959,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1212</v>
+        <v>1832</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -8167,7 +10027,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1213</v>
+        <v>1833</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -8235,7 +10095,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1214</v>
+        <v>1834</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -8303,7 +10163,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1215</v>
+        <v>1835</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -8371,7 +10231,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1216</v>
+        <v>1836</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -8439,7 +10299,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1217</v>
+        <v>1837</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -8752,7 +10612,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1218</v>
+        <v>1838</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -8820,7 +10680,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1219</v>
+        <v>1839</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -8888,7 +10748,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1220</v>
+        <v>1840</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -8956,7 +10816,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1221</v>
+        <v>1841</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -9024,7 +10884,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1222</v>
+        <v>1842</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -9092,7 +10952,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1223</v>
+        <v>1843</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -9160,7 +11020,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1224</v>
+        <v>1844</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -9228,7 +11088,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1225</v>
+        <v>1845</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -9296,7 +11156,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1226</v>
+        <v>1846</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -9609,7 +11469,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1227</v>
+        <v>1847</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -9677,7 +11537,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1228</v>
+        <v>1848</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -9745,7 +11605,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1229</v>
+        <v>1849</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -9813,7 +11673,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1230</v>
+        <v>1850</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -9881,7 +11741,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1231</v>
+        <v>1851</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -9949,7 +11809,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1232</v>
+        <v>1852</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -10017,7 +11877,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1233</v>
+        <v>1853</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -10085,7 +11945,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1234</v>
+        <v>1854</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -10153,7 +12013,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1235</v>
+        <v>1855</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -10469,7 +12329,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1236</v>
+        <v>1856</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -10537,7 +12397,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1237</v>
+        <v>1857</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -10605,7 +12465,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1238</v>
+        <v>1858</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -10673,7 +12533,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1239</v>
+        <v>1859</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -10741,7 +12601,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1240</v>
+        <v>1860</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -10809,7 +12669,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1241</v>
+        <v>1861</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -10877,7 +12737,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1242</v>
+        <v>1862</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -10945,7 +12805,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1243</v>
+        <v>1863</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -11013,7 +12873,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1244</v>
+        <v>1864</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -11328,7 +13188,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1245</v>
+        <v>1865</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -11396,7 +13256,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1246</v>
+        <v>1866</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -11464,7 +13324,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1247</v>
+        <v>1867</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -11532,7 +13392,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1248</v>
+        <v>1868</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -11600,7 +13460,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1249</v>
+        <v>1869</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -11668,7 +13528,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1250</v>
+        <v>1870</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -11736,7 +13596,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1251</v>
+        <v>1871</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -11804,7 +13664,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1252</v>
+        <v>1872</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -11872,7 +13732,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1253</v>
+        <v>1873</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -12186,7 +14046,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1254</v>
+        <v>1874</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -12254,7 +14114,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1255</v>
+        <v>1875</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -12322,7 +14182,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1256</v>
+        <v>1876</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -12390,7 +14250,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1257</v>
+        <v>1877</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -12458,7 +14318,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1258</v>
+        <v>1878</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -12526,7 +14386,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1259</v>
+        <v>1879</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -12594,7 +14454,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1260</v>
+        <v>1880</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -12662,7 +14522,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1261</v>
+        <v>1881</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -12730,7 +14590,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1262</v>
+        <v>1882</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -13044,7 +14904,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1263</v>
+        <v>1883</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -13112,7 +14972,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1264</v>
+        <v>1884</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -13180,7 +15040,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1265</v>
+        <v>1885</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -13248,7 +15108,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1266</v>
+        <v>1886</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -13316,7 +15176,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1267</v>
+        <v>1887</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -13384,7 +15244,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1268</v>
+        <v>1888</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -13452,7 +15312,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1269</v>
+        <v>1889</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -13520,7 +15380,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1270</v>
+        <v>1890</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -13588,7 +15448,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1271</v>
+        <v>1891</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -13896,7 +15756,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1017</v>
+        <v>1637</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -13963,7 +15823,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1018</v>
+        <v>1638</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -14030,7 +15890,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1019</v>
+        <v>1639</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -14094,10 +15954,10 @@
     </row>
     <row ht="72" r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>1020</v>
+        <v>1640</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -14164,7 +16024,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1021</v>
+        <v>1641</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -14231,7 +16091,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1022</v>
+        <v>1642</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -14295,10 +16155,10 @@
     </row>
     <row ht="72" r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>1023</v>
+        <v>1643</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -14365,7 +16225,7 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>1024</v>
+        <v>1644</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -14432,7 +16292,7 @@
         <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>1025</v>
+        <v>1645</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -14496,10 +16356,10 @@
     </row>
     <row ht="72" r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1026</v>
+        <v>1646</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -14563,10 +16423,10 @@
     </row>
     <row ht="72" r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>1027</v>
+        <v>1647</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -14633,7 +16493,7 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>1028</v>
+        <v>1648</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -14700,7 +16560,7 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>1029</v>
+        <v>1649</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -14767,7 +16627,7 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>1030</v>
+        <v>1650</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -14831,10 +16691,10 @@
     </row>
     <row ht="72" r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>1031</v>
+        <v>1651</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -14898,10 +16758,10 @@
     </row>
     <row ht="72" r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>1032</v>
+        <v>1652</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -14968,7 +16828,7 @@
         <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>1033</v>
+        <v>1653</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -15035,7 +16895,7 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>1034</v>
+        <v>1654</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -15102,7 +16962,7 @@
         <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>1035</v>
+        <v>1655</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -15169,7 +17029,7 @@
         <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>1036</v>
+        <v>1656</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -15236,7 +17096,7 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>1037</v>
+        <v>1657</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -15303,7 +17163,7 @@
         <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>1038</v>
+        <v>1658</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -15367,10 +17227,10 @@
     </row>
     <row ht="72" r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>1039</v>
+        <v>1659</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -15434,10 +17294,10 @@
     </row>
     <row ht="72" r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>1040</v>
+        <v>1660</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -15501,10 +17361,10 @@
     </row>
     <row ht="72" r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>1041</v>
+        <v>1661</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -15571,7 +17431,7 @@
         <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>1042</v>
+        <v>1662</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -15635,10 +17495,10 @@
     </row>
     <row ht="72" r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>1043</v>
+        <v>1663</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -15705,7 +17565,7 @@
         <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>1044</v>
+        <v>1664</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -15772,7 +17632,7 @@
         <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>1045</v>
+        <v>1665</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -15839,7 +17699,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>1046</v>
+        <v>1666</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -15906,7 +17766,7 @@
         <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>1047</v>
+        <v>1667</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -15973,7 +17833,7 @@
         <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>1048</v>
+        <v>1668</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -16040,7 +17900,7 @@
         <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>1049</v>
+        <v>1669</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -16107,7 +17967,7 @@
         <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>1050</v>
+        <v>1670</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -16171,10 +18031,10 @@
     </row>
     <row ht="72" r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>1051</v>
+        <v>1671</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -16241,7 +18101,7 @@
         <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>1052</v>
+        <v>1672</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -16308,7 +18168,7 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>1053</v>
+        <v>1673</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -16375,7 +18235,7 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>1054</v>
+        <v>1674</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -16442,7 +18302,7 @@
         <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>1055</v>
+        <v>1675</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -16506,10 +18366,10 @@
     </row>
     <row ht="72" r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>1056</v>
+        <v>1676</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -16573,10 +18433,10 @@
     </row>
     <row ht="72" r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>1057</v>
+        <v>1677</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -16643,7 +18503,7 @@
         <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>1058</v>
+        <v>1678</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -16710,7 +18570,7 @@
         <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>1059</v>
+        <v>1679</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -16774,10 +18634,10 @@
     </row>
     <row ht="72" r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>1060</v>
+        <v>1680</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -16844,7 +18704,7 @@
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>1061</v>
+        <v>1681</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -16911,7 +18771,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>1062</v>
+        <v>1682</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -16975,10 +18835,10 @@
     </row>
     <row ht="72" r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>1063</v>
+        <v>1683</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -17045,7 +18905,7 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>1064</v>
+        <v>1684</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -17109,10 +18969,10 @@
     </row>
     <row ht="72" r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>1065</v>
+        <v>1685</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -17295,7 +19155,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1066</v>
+        <v>1686</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -17359,10 +19219,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>1067</v>
+        <v>1687</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -17426,10 +19286,10 @@
     </row>
     <row ht="72" r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1068</v>
+        <v>1688</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -17493,10 +19353,10 @@
     </row>
     <row ht="72" r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1069</v>
+        <v>1689</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -17563,7 +19423,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1070</v>
+        <v>1690</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -17630,7 +19490,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1071</v>
+        <v>1691</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -17694,10 +19554,10 @@
     </row>
     <row ht="72" r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1072</v>
+        <v>1692</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -17761,10 +19621,10 @@
     </row>
     <row ht="72" r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1073</v>
+        <v>1693</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -17828,10 +19688,10 @@
     </row>
     <row ht="72" r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1074</v>
+        <v>1694</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -17898,7 +19758,7 @@
         <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>1075</v>
+        <v>1695</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -17965,7 +19825,7 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>1076</v>
+        <v>1696</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -18032,7 +19892,7 @@
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>1077</v>
+        <v>1697</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -18099,7 +19959,7 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>1078</v>
+        <v>1698</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -18166,7 +20026,7 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>1079</v>
+        <v>1699</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -18230,10 +20090,10 @@
     </row>
     <row ht="72" r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>1080</v>
+        <v>1700</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -18297,10 +20157,10 @@
     </row>
     <row ht="72" r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>1081</v>
+        <v>1701</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -18364,10 +20224,10 @@
     </row>
     <row ht="72" r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>1082</v>
+        <v>1702</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -18434,7 +20294,7 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>1083</v>
+        <v>1703</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -18501,7 +20361,7 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>1084</v>
+        <v>1704</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -18568,7 +20428,7 @@
         <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>1085</v>
+        <v>1705</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -18635,7 +20495,7 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>1086</v>
+        <v>1706</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -18702,7 +20562,7 @@
         <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>1087</v>
+        <v>1707</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -18769,7 +20629,7 @@
         <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>1088</v>
+        <v>1708</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -18833,10 +20693,10 @@
     </row>
     <row ht="72" r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>1089</v>
+        <v>1709</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -18903,7 +20763,7 @@
         <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>1090</v>
+        <v>1710</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -18967,10 +20827,10 @@
     </row>
     <row ht="72" r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>1091</v>
+        <v>1711</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -19037,7 +20897,7 @@
         <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>1092</v>
+        <v>1712</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -19104,7 +20964,7 @@
         <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>1093</v>
+        <v>1713</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -19171,7 +21031,7 @@
         <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>1094</v>
+        <v>1714</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -19238,7 +21098,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>1095</v>
+        <v>1715</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -19305,7 +21165,7 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>1096</v>
+        <v>1716</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -19372,7 +21232,7 @@
         <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>1097</v>
+        <v>1717</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -19439,7 +21299,7 @@
         <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>1098</v>
+        <v>1718</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -19506,7 +21366,7 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>1099</v>
+        <v>1719</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -19573,7 +21433,7 @@
         <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>1100</v>
+        <v>1720</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -19637,10 +21497,10 @@
     </row>
     <row ht="72" r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>1101</v>
+        <v>1721</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -19707,7 +21567,7 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>1102</v>
+        <v>1722</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -19774,7 +21634,7 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>1103</v>
+        <v>1723</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -19838,10 +21698,10 @@
     </row>
     <row ht="72" r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>1104</v>
+        <v>1724</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -19905,10 +21765,10 @@
     </row>
     <row ht="72" r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>1105</v>
+        <v>1725</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -19972,10 +21832,10 @@
     </row>
     <row ht="72" r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>1106</v>
+        <v>1726</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -20042,7 +21902,7 @@
         <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>1107</v>
+        <v>1727</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -20109,7 +21969,7 @@
         <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>1108</v>
+        <v>1728</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -20173,10 +22033,10 @@
     </row>
     <row ht="72" r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>1109</v>
+        <v>1729</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -20243,7 +22103,7 @@
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>1110</v>
+        <v>1730</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -20310,7 +22170,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>1111</v>
+        <v>1731</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -20374,10 +22234,10 @@
     </row>
     <row ht="72" r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>1112</v>
+        <v>1732</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -20441,10 +22301,10 @@
     </row>
     <row ht="72" r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>1113</v>
+        <v>1733</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -20508,10 +22368,10 @@
     </row>
     <row ht="72" r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>1114</v>
+        <v>1734</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -20698,7 +22558,7 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>1115</v>
+        <v>1735</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -20765,7 +22625,7 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>1116</v>
+        <v>1736</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -20832,7 +22692,7 @@
         <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>1117</v>
+        <v>1737</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -20899,7 +22759,7 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>1118</v>
+        <v>1738</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -20966,7 +22826,7 @@
         <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>1119</v>
+        <v>1739</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -21033,7 +22893,7 @@
         <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>1120</v>
+        <v>1740</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -21100,7 +22960,7 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>1121</v>
+        <v>1741</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -21167,7 +23027,7 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>1122</v>
+        <v>1742</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -21234,7 +23094,7 @@
         <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>1123</v>
+        <v>1743</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -21301,7 +23161,7 @@
         <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>1124</v>
+        <v>1744</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -21368,7 +23228,7 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>1125</v>
+        <v>1745</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -21435,7 +23295,7 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>1126</v>
+        <v>1746</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -21502,7 +23362,7 @@
         <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>1127</v>
+        <v>1747</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -21569,7 +23429,7 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>1128</v>
+        <v>1748</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -21636,7 +23496,7 @@
         <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>1129</v>
+        <v>1749</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -21703,7 +23563,7 @@
         <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>1130</v>
+        <v>1750</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -21770,7 +23630,7 @@
         <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>1131</v>
+        <v>1751</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -21837,7 +23697,7 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>1132</v>
+        <v>1752</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -21904,7 +23764,7 @@
         <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>1133</v>
+        <v>1753</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -21971,7 +23831,7 @@
         <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>1134</v>
+        <v>1754</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -22038,7 +23898,7 @@
         <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>1135</v>
+        <v>1755</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -22105,7 +23965,7 @@
         <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>1136</v>
+        <v>1756</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -22172,7 +24032,7 @@
         <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>1137</v>
+        <v>1757</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -22239,7 +24099,7 @@
         <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>1138</v>
+        <v>1758</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -22306,7 +24166,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>1139</v>
+        <v>1759</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -22373,7 +24233,7 @@
         <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>1140</v>
+        <v>1760</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -22440,7 +24300,7 @@
         <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>1141</v>
+        <v>1761</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -22507,7 +24367,7 @@
         <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>1142</v>
+        <v>1762</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -22574,7 +24434,7 @@
         <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>1143</v>
+        <v>1763</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -22641,7 +24501,7 @@
         <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>1144</v>
+        <v>1764</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -22708,7 +24568,7 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>1145</v>
+        <v>1765</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -22775,7 +24635,7 @@
         <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>1146</v>
+        <v>1766</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -22842,7 +24702,7 @@
         <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>1147</v>
+        <v>1767</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -22909,7 +24769,7 @@
         <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>1148</v>
+        <v>1768</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -22976,7 +24836,7 @@
         <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>1149</v>
+        <v>1769</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -23043,7 +24903,7 @@
         <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>1150</v>
+        <v>1770</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -23110,7 +24970,7 @@
         <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>1151</v>
+        <v>1771</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -23177,7 +25037,7 @@
         <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>1152</v>
+        <v>1772</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -23244,7 +25104,7 @@
         <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>1153</v>
+        <v>1773</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -23311,7 +25171,7 @@
         <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>1154</v>
+        <v>1774</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -23378,7 +25238,7 @@
         <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>1155</v>
+        <v>1775</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -23445,7 +25305,7 @@
         <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>1156</v>
+        <v>1776</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -23512,7 +25372,7 @@
         <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>1157</v>
+        <v>1777</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -23579,7 +25439,7 @@
         <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>1158</v>
+        <v>1778</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -23646,7 +25506,7 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>1159</v>
+        <v>1779</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -23713,7 +25573,7 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>1160</v>
+        <v>1780</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -23780,7 +25640,7 @@
         <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>1161</v>
+        <v>1781</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -23847,7 +25707,7 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>1162</v>
+        <v>1782</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -23914,7 +25774,7 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>1163</v>
+        <v>1783</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -24105,7 +25965,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1164</v>
+        <v>1784</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -24169,10 +26029,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>1165</v>
+        <v>1785</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -24239,7 +26099,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1166</v>
+        <v>1786</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -24306,7 +26166,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1167</v>
+        <v>1787</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -24373,7 +26233,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1168</v>
+        <v>1788</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -24440,7 +26300,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1169</v>
+        <v>1789</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -24504,10 +26364,10 @@
     </row>
     <row ht="72" r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1170</v>
+        <v>1790</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -24574,7 +26434,7 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>1171</v>
+        <v>1791</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -24641,7 +26501,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1172</v>
+        <v>1792</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -24952,7 +26812,7 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>1173</v>
+        <v>1793</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -25019,7 +26879,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1174</v>
+        <v>1794</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -25083,10 +26943,10 @@
     </row>
     <row ht="72" r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1175</v>
+        <v>1795</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -25153,7 +27013,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1176</v>
+        <v>1796</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -25220,7 +27080,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1177</v>
+        <v>1797</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -25287,7 +27147,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1178</v>
+        <v>1798</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -25354,7 +27214,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1179</v>
+        <v>1799</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -25418,10 +27278,10 @@
     </row>
     <row ht="72" r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>1180</v>
+        <v>1800</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -25488,7 +27348,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1181</v>
+        <v>1801</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -25799,7 +27659,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1182</v>
+        <v>1802</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -25866,7 +27726,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1183</v>
+        <v>1803</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -25933,7 +27793,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1184</v>
+        <v>1804</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -26000,7 +27860,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1185</v>
+        <v>1805</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -26067,7 +27927,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1186</v>
+        <v>1806</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -26134,7 +27994,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1187</v>
+        <v>1807</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -26201,7 +28061,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1188</v>
+        <v>1808</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -26268,7 +28128,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1189</v>
+        <v>1809</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -26335,7 +28195,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1190</v>
+        <v>1810</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -26646,7 +28506,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1191</v>
+        <v>1811</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -26713,7 +28573,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1192</v>
+        <v>1812</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -26780,7 +28640,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1193</v>
+        <v>1813</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -26847,7 +28707,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1194</v>
+        <v>1814</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -26914,7 +28774,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1195</v>
+        <v>1815</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -26981,7 +28841,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1196</v>
+        <v>1816</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -27048,7 +28908,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1197</v>
+        <v>1817</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -27115,7 +28975,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1198</v>
+        <v>1818</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -27182,7 +29042,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1199</v>
+        <v>1819</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -27495,7 +29355,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1200</v>
+        <v>1820</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -27563,7 +29423,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1201</v>
+        <v>1821</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -27631,7 +29491,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1202</v>
+        <v>1822</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -27699,7 +29559,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1203</v>
+        <v>1823</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -27767,7 +29627,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1204</v>
+        <v>1824</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -27835,7 +29695,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1205</v>
+        <v>1825</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -27903,7 +29763,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1206</v>
+        <v>1826</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -27971,7 +29831,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1207</v>
+        <v>1827</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -28039,7 +29899,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1208</v>
+        <v>1828</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>

--- a/KatalonData/IWPTestData/DisplayCFDataDemo.xlsx
+++ b/KatalonData/IWPTestData/DisplayCFDataDemo.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11076" uniqueCount="1892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12248" uniqueCount="2185">
   <si>
     <t>Result</t>
   </si>
@@ -5716,6 +5716,885 @@
   </si>
   <si>
     <t>Mon Feb 23 08:51:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:24:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:27:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:29:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:31:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:32:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:34:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:35:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:36:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:38:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:39:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:41:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:42:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:45:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:47:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:48:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:50:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:51:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:53:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:54:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:56:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:59:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:00:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:02:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:03:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:05:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:06:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:08:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:09:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:10:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:12:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:13:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:16:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:21:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:23:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:26:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:28:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:31:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:33:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:35:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:36:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:38:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:39:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:41:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:42:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:44:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:46:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:48:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:49:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:52:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:54:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:56:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:57:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:58:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:00:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:01:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:03:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:04:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:05:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:06:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:07:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:09:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:10:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:12:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:14:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:15:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:16:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:17:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:18:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:20:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:21:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:22:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:23:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:25:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:26:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:28:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:29:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:32:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:33:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:36:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:38:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:41:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:43:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:48:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:51:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:54:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:55:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:56:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:57:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:58:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:00:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:01:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:03:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:04:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:06:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:10:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:11:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:12:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:14:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:15:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:17:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:18:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:19:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:20:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:21:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:22:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:23:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:25:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:26:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:28:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:28:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:30:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:31:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:33:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:34:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:36:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:37:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:38:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:39:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:41:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:42:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:43:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:45:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:47:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:48:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:49:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:51:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:53:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:55:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:58:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:01:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:03:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:06:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:08:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:10:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:12:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:13:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:14:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:16:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:17:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:21:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:23:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:24:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:25:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:26:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:27:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:28:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:29:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:30:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:31:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:32:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:33:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:34:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:35:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:36:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:37:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:38:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:39:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:40:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:42:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:43:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:44:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:45:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:46:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:47:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:48:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:49:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:50:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:51:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:52:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:53:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:54:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:55:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:56:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 05:59:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:01:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:04:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:06:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:09:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:14:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:16:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:18:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:19:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:20:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:21:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:22:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:23:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:24:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:25:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:26:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:31:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:35:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:39:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:43:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:47:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:52:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 06:56:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:00:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:05:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:09:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:13:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:17:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:21:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:25:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:29:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:33:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:38:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:42:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:46:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:50:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:54:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 07:58:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:02:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:06:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:11:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:15:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:19:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:23:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:27:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:31:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:35:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:39:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:43:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:47:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:50:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:54:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 08:57:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:00:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:06:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:12:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:14:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:17:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:20:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:23:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:26:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:29:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:32:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:35:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:38:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:41:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:44:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:47:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:50:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:54:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 09:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:00:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:06:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:11:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:16:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:22:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:27:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:30:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:33:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:36:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:39:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:44:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:49:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 10:55:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:00:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:04:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:07:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:10:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:13:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:16:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:18:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:21:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:24:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:27:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:30:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:33:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:36:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:39:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:45:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:47:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:50:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:54:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 11:57:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 12:00:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 12:03:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 12:06:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 12:09:09 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -6216,7 +7095,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1586</v>
+        <v>1892</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -6283,7 +7162,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1587</v>
+        <v>1893</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -6350,7 +7229,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1588</v>
+        <v>1894</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -6417,7 +7296,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1589</v>
+        <v>1895</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -6484,7 +7363,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1590</v>
+        <v>1896</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -6551,7 +7430,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1591</v>
+        <v>1897</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -6618,7 +7497,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1592</v>
+        <v>1898</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -6685,7 +7564,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1593</v>
+        <v>1899</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -6752,7 +7631,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1594</v>
+        <v>1900</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -6819,7 +7698,7 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1595</v>
+        <v>1901</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -6886,7 +7765,7 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>1596</v>
+        <v>1902</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -6953,7 +7832,7 @@
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>1597</v>
+        <v>1903</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -7020,7 +7899,7 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>1598</v>
+        <v>1904</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -7087,7 +7966,7 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>1599</v>
+        <v>1905</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -7154,7 +8033,7 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>1600</v>
+        <v>1906</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -7221,7 +8100,7 @@
         <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>1601</v>
+        <v>1907</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -7288,7 +8167,7 @@
         <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>1602</v>
+        <v>1908</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -7355,7 +8234,7 @@
         <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>1603</v>
+        <v>1909</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -7422,7 +8301,7 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>1604</v>
+        <v>1910</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -7489,7 +8368,7 @@
         <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>1605</v>
+        <v>1911</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -7556,7 +8435,7 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>1606</v>
+        <v>1912</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -7623,7 +8502,7 @@
         <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>1607</v>
+        <v>1913</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -7690,7 +8569,7 @@
         <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>1608</v>
+        <v>1914</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -7757,7 +8636,7 @@
         <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>1609</v>
+        <v>1915</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -7824,7 +8703,7 @@
         <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>1610</v>
+        <v>1916</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -7891,7 +8770,7 @@
         <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>1611</v>
+        <v>1917</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -7958,7 +8837,7 @@
         <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>1612</v>
+        <v>1918</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -8025,7 +8904,7 @@
         <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>1613</v>
+        <v>1919</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -8092,7 +8971,7 @@
         <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>1614</v>
+        <v>1920</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -8159,7 +9038,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>1615</v>
+        <v>1921</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -8226,7 +9105,7 @@
         <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>1616</v>
+        <v>1922</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -8293,7 +9172,7 @@
         <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>1617</v>
+        <v>1923</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -8360,7 +9239,7 @@
         <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>1618</v>
+        <v>1924</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -8427,7 +9306,7 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>1619</v>
+        <v>1925</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -8494,7 +9373,7 @@
         <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>1620</v>
+        <v>1926</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -8561,7 +9440,7 @@
         <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>1621</v>
+        <v>1927</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -8628,7 +9507,7 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>1622</v>
+        <v>1928</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -8695,7 +9574,7 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>1623</v>
+        <v>1929</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -8762,7 +9641,7 @@
         <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>1624</v>
+        <v>1930</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -8829,7 +9708,7 @@
         <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>1625</v>
+        <v>1931</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -8896,7 +9775,7 @@
         <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>1626</v>
+        <v>1932</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -8963,7 +9842,7 @@
         <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>1627</v>
+        <v>1933</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -9030,7 +9909,7 @@
         <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>1628</v>
+        <v>1934</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -9097,7 +9976,7 @@
         <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>1629</v>
+        <v>1935</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -9164,7 +10043,7 @@
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>1630</v>
+        <v>1936</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -9231,7 +10110,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>1631</v>
+        <v>1937</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -9298,7 +10177,7 @@
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>1632</v>
+        <v>1938</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -9365,7 +10244,7 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>1633</v>
+        <v>1939</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -9432,7 +10311,7 @@
         <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>1634</v>
+        <v>1940</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>96</v>
@@ -9499,7 +10378,7 @@
         <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>1635</v>
+        <v>1941</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>91</v>
@@ -9563,10 +10442,10 @@
     </row>
     <row ht="115.2" r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>1636</v>
+        <v>1942</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>97</v>
@@ -9755,7 +10634,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1829</v>
+        <v>2135</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -9823,7 +10702,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1830</v>
+        <v>2136</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -9891,7 +10770,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1831</v>
+        <v>2137</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -9959,7 +10838,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1832</v>
+        <v>2138</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -10027,7 +10906,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1833</v>
+        <v>2139</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -10095,7 +10974,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1834</v>
+        <v>2140</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -10163,7 +11042,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1835</v>
+        <v>2141</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -10231,7 +11110,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1836</v>
+        <v>2142</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -10299,7 +11178,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1837</v>
+        <v>2143</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -10612,7 +11491,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1838</v>
+        <v>2144</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -10680,7 +11559,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1839</v>
+        <v>2145</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -10748,7 +11627,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1840</v>
+        <v>2146</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -10816,7 +11695,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1841</v>
+        <v>2147</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -10884,7 +11763,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1842</v>
+        <v>2148</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -10952,7 +11831,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1843</v>
+        <v>2149</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -11020,7 +11899,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1844</v>
+        <v>2150</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -11088,7 +11967,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1845</v>
+        <v>2151</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -11156,7 +12035,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1846</v>
+        <v>2152</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -11469,7 +12348,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1847</v>
+        <v>2153</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -11537,7 +12416,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1848</v>
+        <v>2154</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -11605,7 +12484,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1849</v>
+        <v>2155</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -11673,7 +12552,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1850</v>
+        <v>2156</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -11741,7 +12620,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1851</v>
+        <v>2157</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -11809,7 +12688,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1852</v>
+        <v>2158</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -11877,7 +12756,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1853</v>
+        <v>2159</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -11945,7 +12824,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1854</v>
+        <v>2160</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -12013,7 +12892,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1855</v>
+        <v>2161</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -12329,7 +13208,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1856</v>
+        <v>2162</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -12397,7 +13276,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1857</v>
+        <v>2163</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -12465,7 +13344,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1858</v>
+        <v>2164</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -12533,7 +13412,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1859</v>
+        <v>2165</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -12601,7 +13480,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1860</v>
+        <v>2166</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -12669,7 +13548,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1861</v>
+        <v>2167</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -12737,7 +13616,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1862</v>
+        <v>2168</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -12805,7 +13684,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1863</v>
+        <v>2169</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -12873,7 +13752,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1864</v>
+        <v>2170</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -13188,7 +14067,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1865</v>
+        <v>2171</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -13256,7 +14135,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1866</v>
+        <v>2172</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -13324,7 +14203,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1867</v>
+        <v>2173</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -13392,7 +14271,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1868</v>
+        <v>2174</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -13460,7 +14339,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1869</v>
+        <v>2175</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -13528,7 +14407,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1870</v>
+        <v>2176</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -13596,7 +14475,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1871</v>
+        <v>2177</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -13664,7 +14543,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1872</v>
+        <v>2178</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -13732,7 +14611,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1873</v>
+        <v>2179</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -14046,7 +14925,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1874</v>
+        <v>2180</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -14114,7 +14993,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1875</v>
+        <v>2181</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -14182,7 +15061,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1876</v>
+        <v>2182</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -14250,7 +15129,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1877</v>
+        <v>2183</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -14318,7 +15197,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1878</v>
+        <v>2184</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -15756,7 +16635,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1637</v>
+        <v>1943</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -15823,7 +16702,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1638</v>
+        <v>1944</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -15890,7 +16769,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1639</v>
+        <v>1945</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -15957,7 +16836,7 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>1640</v>
+        <v>1946</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -16024,7 +16903,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1641</v>
+        <v>1947</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -16091,7 +16970,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1642</v>
+        <v>1948</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -16155,10 +17034,10 @@
     </row>
     <row ht="72" r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1643</v>
+        <v>1949</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -16222,10 +17101,10 @@
     </row>
     <row ht="72" r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1644</v>
+        <v>1950</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -16289,10 +17168,10 @@
     </row>
     <row ht="72" r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1645</v>
+        <v>1951</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -16356,10 +17235,10 @@
     </row>
     <row ht="72" r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>1646</v>
+        <v>1952</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -16423,10 +17302,10 @@
     </row>
     <row ht="72" r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>1647</v>
+        <v>1953</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -16493,7 +17372,7 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>1648</v>
+        <v>1954</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -16560,7 +17439,7 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>1649</v>
+        <v>1955</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -16627,7 +17506,7 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>1650</v>
+        <v>1956</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -16694,7 +17573,7 @@
         <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>1651</v>
+        <v>1957</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -16758,10 +17637,10 @@
     </row>
     <row ht="72" r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>1652</v>
+        <v>1958</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -16828,7 +17707,7 @@
         <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>1653</v>
+        <v>1959</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -16895,7 +17774,7 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>1654</v>
+        <v>1960</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -16962,7 +17841,7 @@
         <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>1655</v>
+        <v>1961</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -17029,7 +17908,7 @@
         <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>1656</v>
+        <v>1962</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -17096,7 +17975,7 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>1657</v>
+        <v>1963</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -17163,7 +18042,7 @@
         <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>1658</v>
+        <v>1964</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -17230,7 +18109,7 @@
         <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>1659</v>
+        <v>1965</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -17297,7 +18176,7 @@
         <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>1660</v>
+        <v>1966</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -17364,7 +18243,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>1661</v>
+        <v>1967</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -17428,10 +18307,10 @@
     </row>
     <row ht="72" r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>1662</v>
+        <v>1968</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -17495,10 +18374,10 @@
     </row>
     <row ht="72" r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>1663</v>
+        <v>1969</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -17562,10 +18441,10 @@
     </row>
     <row ht="72" r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>1664</v>
+        <v>1970</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -17632,7 +18511,7 @@
         <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>1665</v>
+        <v>1971</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -17699,7 +18578,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>1666</v>
+        <v>1972</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -17766,7 +18645,7 @@
         <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>1667</v>
+        <v>1973</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -17833,7 +18712,7 @@
         <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>1668</v>
+        <v>1974</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -17897,10 +18776,10 @@
     </row>
     <row ht="72" r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>1669</v>
+        <v>1975</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -17964,10 +18843,10 @@
     </row>
     <row ht="72" r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>1670</v>
+        <v>1976</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -18031,10 +18910,10 @@
     </row>
     <row ht="72" r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>1671</v>
+        <v>1977</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -18098,10 +18977,10 @@
     </row>
     <row ht="72" r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>1672</v>
+        <v>1978</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -18168,7 +19047,7 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>1673</v>
+        <v>1979</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -18235,7 +19114,7 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>1674</v>
+        <v>1980</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -18299,10 +19178,10 @@
     </row>
     <row ht="72" r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>1675</v>
+        <v>1981</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -18366,10 +19245,10 @@
     </row>
     <row ht="72" r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>1676</v>
+        <v>1982</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -18436,7 +19315,7 @@
         <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>1677</v>
+        <v>1983</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -18500,10 +19379,10 @@
     </row>
     <row ht="72" r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>1678</v>
+        <v>1984</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -18570,7 +19449,7 @@
         <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>1679</v>
+        <v>1985</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -18634,10 +19513,10 @@
     </row>
     <row ht="72" r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>1680</v>
+        <v>1986</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -18704,7 +19583,7 @@
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>1681</v>
+        <v>1987</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -18771,7 +19650,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>1682</v>
+        <v>1988</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -18838,7 +19717,7 @@
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>1683</v>
+        <v>1989</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -18905,7 +19784,7 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>1684</v>
+        <v>1990</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -18969,10 +19848,10 @@
     </row>
     <row ht="72" r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>1685</v>
+        <v>1991</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -19155,7 +20034,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1686</v>
+        <v>1992</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -19222,7 +20101,7 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>1687</v>
+        <v>1993</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -19286,10 +20165,10 @@
     </row>
     <row ht="72" r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>1688</v>
+        <v>1994</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -19356,7 +20235,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1689</v>
+        <v>1995</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -19423,7 +20302,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1690</v>
+        <v>1996</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -19490,7 +20369,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1691</v>
+        <v>1997</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -19554,10 +20433,10 @@
     </row>
     <row ht="72" r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>1692</v>
+        <v>1998</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -19621,10 +20500,10 @@
     </row>
     <row ht="72" r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>1693</v>
+        <v>1999</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -19691,7 +20570,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1694</v>
+        <v>2000</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -19755,10 +20634,10 @@
     </row>
     <row ht="72" r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>1695</v>
+        <v>2001</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -19822,10 +20701,10 @@
     </row>
     <row ht="72" r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>1696</v>
+        <v>2002</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -19889,10 +20768,10 @@
     </row>
     <row ht="72" r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>1697</v>
+        <v>2003</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -19959,7 +20838,7 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>1698</v>
+        <v>2004</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -20026,7 +20905,7 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>1699</v>
+        <v>2005</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -20093,7 +20972,7 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>1700</v>
+        <v>2006</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -20160,7 +21039,7 @@
         <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>1701</v>
+        <v>2007</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -20227,7 +21106,7 @@
         <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>1702</v>
+        <v>2008</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -20294,7 +21173,7 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>1703</v>
+        <v>2009</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -20361,7 +21240,7 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>1704</v>
+        <v>2010</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -20425,10 +21304,10 @@
     </row>
     <row ht="72" r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>1705</v>
+        <v>2011</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -20495,7 +21374,7 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>1706</v>
+        <v>2012</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -20562,7 +21441,7 @@
         <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>1707</v>
+        <v>2013</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -20629,7 +21508,7 @@
         <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>1708</v>
+        <v>2014</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -20693,10 +21572,10 @@
     </row>
     <row ht="72" r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>1709</v>
+        <v>2015</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -20763,7 +21642,7 @@
         <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>1710</v>
+        <v>2016</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -20827,10 +21706,10 @@
     </row>
     <row ht="72" r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>1711</v>
+        <v>2017</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -20894,10 +21773,10 @@
     </row>
     <row ht="72" r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>1712</v>
+        <v>2018</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -20964,7 +21843,7 @@
         <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>1713</v>
+        <v>2019</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -21031,7 +21910,7 @@
         <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>1714</v>
+        <v>2020</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -21098,7 +21977,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>1715</v>
+        <v>2021</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -21162,10 +22041,10 @@
     </row>
     <row ht="72" r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>1716</v>
+        <v>2022</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -21229,10 +22108,10 @@
     </row>
     <row ht="72" r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>1717</v>
+        <v>2023</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -21296,10 +22175,10 @@
     </row>
     <row ht="72" r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>1718</v>
+        <v>2024</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -21366,7 +22245,7 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>1719</v>
+        <v>2025</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -21430,10 +22309,10 @@
     </row>
     <row ht="72" r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>1720</v>
+        <v>2026</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -21500,7 +22379,7 @@
         <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>1721</v>
+        <v>2027</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -21567,7 +22446,7 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>1722</v>
+        <v>2028</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -21634,7 +22513,7 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>1723</v>
+        <v>2029</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -21701,7 +22580,7 @@
         <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>1724</v>
+        <v>2030</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -21768,7 +22647,7 @@
         <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>1725</v>
+        <v>2031</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -21835,7 +22714,7 @@
         <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>1726</v>
+        <v>2032</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -21899,10 +22778,10 @@
     </row>
     <row ht="72" r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>1727</v>
+        <v>2033</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -21969,7 +22848,7 @@
         <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>1728</v>
+        <v>2034</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -22033,10 +22912,10 @@
     </row>
     <row ht="72" r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>1729</v>
+        <v>2035</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -22103,7 +22982,7 @@
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>1730</v>
+        <v>2036</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -22170,7 +23049,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>1731</v>
+        <v>2037</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -22237,7 +23116,7 @@
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>1732</v>
+        <v>2038</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -22304,7 +23183,7 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>1733</v>
+        <v>2039</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -22368,10 +23247,10 @@
     </row>
     <row ht="72" r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>1734</v>
+        <v>2040</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -22558,7 +23437,7 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>1735</v>
+        <v>2041</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -22625,7 +23504,7 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>1736</v>
+        <v>2042</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -22692,7 +23571,7 @@
         <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>1737</v>
+        <v>2043</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -22759,7 +23638,7 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>1738</v>
+        <v>2044</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -22826,7 +23705,7 @@
         <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>1739</v>
+        <v>2045</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -22893,7 +23772,7 @@
         <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>1740</v>
+        <v>2046</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -22960,7 +23839,7 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>1741</v>
+        <v>2047</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -23027,7 +23906,7 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>1742</v>
+        <v>2048</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -23094,7 +23973,7 @@
         <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>1743</v>
+        <v>2049</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -23161,7 +24040,7 @@
         <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>1744</v>
+        <v>2050</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -23228,7 +24107,7 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>1745</v>
+        <v>2051</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -23295,7 +24174,7 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>1746</v>
+        <v>2052</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -23362,7 +24241,7 @@
         <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>1747</v>
+        <v>2053</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -23429,7 +24308,7 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>1748</v>
+        <v>2054</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -23496,7 +24375,7 @@
         <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>1749</v>
+        <v>2055</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -23563,7 +24442,7 @@
         <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>1750</v>
+        <v>2056</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -23630,7 +24509,7 @@
         <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>1751</v>
+        <v>2057</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -23697,7 +24576,7 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>1752</v>
+        <v>2058</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -23764,7 +24643,7 @@
         <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>1753</v>
+        <v>2059</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -23831,7 +24710,7 @@
         <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>1754</v>
+        <v>2060</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -23898,7 +24777,7 @@
         <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>1755</v>
+        <v>2061</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -23965,7 +24844,7 @@
         <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>1756</v>
+        <v>2062</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -24032,7 +24911,7 @@
         <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>1757</v>
+        <v>2063</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -24099,7 +24978,7 @@
         <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>1758</v>
+        <v>2064</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -24166,7 +25045,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>1759</v>
+        <v>2065</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -24233,7 +25112,7 @@
         <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>1760</v>
+        <v>2066</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -24300,7 +25179,7 @@
         <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>1761</v>
+        <v>2067</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -24367,7 +25246,7 @@
         <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>1762</v>
+        <v>2068</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -24434,7 +25313,7 @@
         <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>1763</v>
+        <v>2069</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -24501,7 +25380,7 @@
         <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>1764</v>
+        <v>2070</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -24568,7 +25447,7 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>1765</v>
+        <v>2071</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -24635,7 +25514,7 @@
         <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>1766</v>
+        <v>2072</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -24699,10 +25578,10 @@
     </row>
     <row ht="72" r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>1767</v>
+        <v>2073</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -24766,10 +25645,10 @@
     </row>
     <row ht="72" r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>1768</v>
+        <v>2074</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -24833,10 +25712,10 @@
     </row>
     <row ht="72" r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>1769</v>
+        <v>2075</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -24900,10 +25779,10 @@
     </row>
     <row ht="72" r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>1770</v>
+        <v>2076</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -24967,10 +25846,10 @@
     </row>
     <row ht="72" r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>1771</v>
+        <v>2077</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -25034,10 +25913,10 @@
     </row>
     <row ht="72" r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>1772</v>
+        <v>2078</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -25101,10 +25980,10 @@
     </row>
     <row ht="72" r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>1773</v>
+        <v>2079</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -25168,10 +26047,10 @@
     </row>
     <row ht="72" r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>1774</v>
+        <v>2080</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -25238,7 +26117,7 @@
         <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>1775</v>
+        <v>2081</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -25305,7 +26184,7 @@
         <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>1776</v>
+        <v>2082</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -25372,7 +26251,7 @@
         <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>1777</v>
+        <v>2083</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -25439,7 +26318,7 @@
         <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>1778</v>
+        <v>2084</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -25506,7 +26385,7 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>1779</v>
+        <v>2085</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -25573,7 +26452,7 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>1780</v>
+        <v>2086</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -25640,7 +26519,7 @@
         <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>1781</v>
+        <v>2087</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -25707,7 +26586,7 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>1782</v>
+        <v>2088</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -25774,7 +26653,7 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>1783</v>
+        <v>2089</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -25965,7 +26844,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1784</v>
+        <v>2090</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -26029,10 +26908,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1785</v>
+        <v>2091</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -26099,7 +26978,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1786</v>
+        <v>2092</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -26166,7 +27045,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1787</v>
+        <v>2093</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -26233,7 +27112,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1788</v>
+        <v>2094</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -26300,7 +27179,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1789</v>
+        <v>2095</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -26367,7 +27246,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1790</v>
+        <v>2096</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -26431,10 +27310,10 @@
     </row>
     <row ht="72" r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1791</v>
+        <v>2097</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -26501,7 +27380,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1792</v>
+        <v>2098</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -26809,10 +27688,10 @@
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1793</v>
+        <v>2099</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -26879,7 +27758,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1794</v>
+        <v>2100</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -26946,7 +27825,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1795</v>
+        <v>2101</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -27013,7 +27892,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1796</v>
+        <v>2102</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -27080,7 +27959,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1797</v>
+        <v>2103</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -27147,7 +28026,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1798</v>
+        <v>2104</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -27214,7 +28093,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1799</v>
+        <v>2105</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -27278,10 +28157,10 @@
     </row>
     <row ht="72" r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1800</v>
+        <v>2106</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -27348,7 +28227,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1801</v>
+        <v>2107</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -27659,7 +28538,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1802</v>
+        <v>2108</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -27726,7 +28605,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1803</v>
+        <v>2109</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -27793,7 +28672,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1804</v>
+        <v>2110</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -27860,7 +28739,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1805</v>
+        <v>2111</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -27927,7 +28806,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1806</v>
+        <v>2112</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -27994,7 +28873,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1807</v>
+        <v>2113</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -28061,7 +28940,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1808</v>
+        <v>2114</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -28128,7 +29007,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1809</v>
+        <v>2115</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -28195,7 +29074,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1810</v>
+        <v>2116</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -28506,7 +29385,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1811</v>
+        <v>2117</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -28573,7 +29452,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1812</v>
+        <v>2118</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -28640,7 +29519,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1813</v>
+        <v>2119</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -28707,7 +29586,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1814</v>
+        <v>2120</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -28774,7 +29653,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1815</v>
+        <v>2121</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -28841,7 +29720,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1816</v>
+        <v>2122</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -28908,7 +29787,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1817</v>
+        <v>2123</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -28975,7 +29854,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1818</v>
+        <v>2124</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -29042,7 +29921,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1819</v>
+        <v>2125</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -29355,7 +30234,7 @@
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>1820</v>
+        <v>2126</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -29423,7 +30302,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>1821</v>
+        <v>2127</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -29491,7 +30370,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>1822</v>
+        <v>2128</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -29559,7 +30438,7 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>1823</v>
+        <v>2129</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -29627,7 +30506,7 @@
         <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>1824</v>
+        <v>2130</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -29695,7 +30574,7 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>1825</v>
+        <v>2131</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -29763,7 +30642,7 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>1826</v>
+        <v>2132</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -29831,7 +30710,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>1827</v>
+        <v>2133</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -29899,7 +30778,7 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>1828</v>
+        <v>2134</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
